--- a/model_analysis/generic_kl_multiple_single_variable_analysis_test_set.xlsx
+++ b/model_analysis/generic_kl_multiple_single_variable_analysis_test_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25460" windowHeight="12700" activeTab="1"/>
+    <workbookView windowWidth="17830" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1168,7 +1168,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1179,7 +1179,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="3" max="3" width="32.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -1686,7 +1690,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="3" width="32.875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2193,7 +2200,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2700,11 +2707,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="43.2727272727273" customWidth="1"/>
-    <col min="2" max="2" width="33.6363636363636" customWidth="1"/>
-    <col min="3" max="3" width="32.4545454545455" customWidth="1"/>
+    <col min="1" max="1" width="43.275" customWidth="1"/>
+    <col min="2" max="2" width="33.6333333333333" customWidth="1"/>
+    <col min="3" max="3" width="32.4583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
